--- a/src/data/COREP_files/G_EU_C_C1800.xlsx
+++ b/src/data/COREP_files/G_EU_C_C1800.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -543,6 +543,9 @@
           <t>TRADED DEBT INSTRUMENTS IN TRADING BOOK</t>
         </is>
       </c>
+      <c r="M10" t="n">
+        <v>19</v>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>Cell linked to CA2</t>
@@ -560,6 +563,12 @@
           <t>General risk</t>
         </is>
       </c>
+      <c r="M11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -871,6 +880,12 @@
         <is>
           <t>Specific risk</t>
         </is>
+      </c>
+      <c r="M37" t="n">
+        <v>25</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="38">
@@ -1006,6 +1021,12 @@
           <t>Own funds requirement for securitisation instruments</t>
         </is>
       </c>
+      <c r="M47" t="n">
+        <v>28</v>
+      </c>
+      <c r="N47" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
@@ -1079,7 +1100,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
